--- a/مراجعة_ورشة_ثروت_المصري.xlsx
+++ b/مراجعة_ورشة_ثروت_المصري.xlsx
@@ -65,7 +65,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -84,6 +84,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F0F8F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF6CC"/>
       </patternFill>
     </fill>
@@ -94,7 +99,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FBD5D5"/>
+        <fgColor rgb="00E4E4F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -138,17 +143,11 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,6 +156,12 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -538,26 +543,26 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="5" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="42" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ورشة ثروت المصري — مراجعة مطابقة الأصناف</t>
+          <t>ورشة ثروت المصري — مراجعة مطابقة الأصناف (محدّثة)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>صحّح عمود «الكود الصحيح» الأصفر فقط · 🟢 مؤكد · 🟡 السعر طابق والاسم مش تماماً · 🔴 مش بالكتالوج</t>
+          <t>صحّح العمود الأصفر «الكود الصحيح» فقط · 🟢 جاهز · 🟡 بدّه تأكيدك · ⏸️ مؤجّل لعائلة كاملة (اتركه فاضي)</t>
         </is>
       </c>
     </row>
@@ -870,7 +875,7 @@
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>🔴</t>
+          <t>⏸️</t>
         </is>
       </c>
       <c r="H10" s="11" t="inlineStr">
@@ -887,7 +892,7 @@
       <c r="K10" s="7" t="n"/>
       <c r="L10" s="10" t="inlineStr">
         <is>
-          <t>روبة تيراكو عندنا 1001/1004/1022 فقط بـ11 — أي رقم هو الأسود؟</t>
+          <t>مؤجّل — عائلة الروبة بدها ترتيب (سافيتو + تيراكو + ألوان بأسعار مختلفة)</t>
         </is>
       </c>
     </row>
@@ -991,45 +996,47 @@
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>ورق حف ماكينة 9"</t>
         </is>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="6" t="n">
         <v>0.4</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>🔴</t>
-        </is>
-      </c>
-      <c r="H13" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J13" s="11" t="inlineStr"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>100358</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>ورق حف دائري 9" نعومة 120</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.5</v>
+      </c>
       <c r="K13" s="7" t="n"/>
-      <c r="L13" s="10" t="inlineStr">
-        <is>
-          <t>ورق حف دائري 9" — أي نعومة؟ (040…220) كلهن بـ0.5</t>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>ورق حف دائري 9" نعومة 120</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1174,7 @@
       <c r="K16" s="7" t="n"/>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>نفس بند 9</t>
+          <t>نفس بند 3</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1470,7 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>29//5/2026</t>
+          <t>⚠️ 29//5/2026</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
@@ -1507,7 +1514,7 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>29//5/2026</t>
+          <t>⚠️ 29//5/2026</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
@@ -1551,7 +1558,7 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>29//5/2026</t>
+          <t>⚠️ 29//5/2026</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
@@ -1757,45 +1764,47 @@
       <c r="A30" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>اجار كمبريسة 50لتر</t>
         </is>
       </c>
-      <c r="C30" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="11" t="n">
+      <c r="C30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="6" t="n">
         <v>10</v>
       </c>
       <c r="E30" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
-        <is>
-          <t>🔴</t>
-        </is>
-      </c>
-      <c r="H30" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I30" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J30" s="11" t="inlineStr"/>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>900923</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>إيجار عدة — كمبريسة هواء 50 لتر</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="K30" s="7" t="n"/>
-      <c r="L30" s="10" t="inlineStr">
-        <is>
-          <t>«اجار كمبريسة» = إيجار؟ مش بالكتالوج — صنف خدمة جديد؟</t>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>صنف خدمة جديد</t>
         </is>
       </c>
     </row>
@@ -1803,93 +1812,91 @@
       <c r="A31" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>معجونه سيليكون لون اسود</t>
         </is>
       </c>
-      <c r="C31" s="9" t="n">
+      <c r="C31" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D31" s="9" t="n">
+      <c r="D31" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>🟡</t>
-        </is>
-      </c>
-      <c r="H31" s="9" t="inlineStr">
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>700103</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>سيليكون اسود 280 غم SK</t>
         </is>
       </c>
-      <c r="J31" s="9" t="n">
+      <c r="J31" s="6" t="n">
         <v>1.5</v>
       </c>
       <c r="K31" s="7" t="n"/>
-      <c r="L31" s="8" t="inlineStr">
-        <is>
-          <t>«سيليكون اسود 280 غم SK» بـ1.5 · وفي «معجونة سيليكون تركي سكني 450غم» بـ1</t>
-        </is>
-      </c>
+      <c r="L31" s="5" t="inlineStr"/>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>معجونه سيليكون لون بيج</t>
         </is>
       </c>
-      <c r="C32" s="11" t="n">
+      <c r="C32" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D32" s="11" t="n">
+      <c r="D32" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E32" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="G32" s="11" t="inlineStr">
-        <is>
-          <t>🔴</t>
-        </is>
-      </c>
-      <c r="H32" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I32" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J32" s="11" t="inlineStr"/>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>702740</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>سيليكون بيج 280 غم SK</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="n">
+        <v>1.5</v>
+      </c>
       <c r="K32" s="7" t="n"/>
-      <c r="L32" s="10" t="inlineStr">
-        <is>
-          <t>سيليكون **بيج** مش بالكتالوج</t>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>صنف جديد — بيع 1.5</t>
         </is>
       </c>
     </row>
@@ -1897,49 +1904,45 @@
       <c r="A33" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>معجونه سيليكون لون ابيض</t>
         </is>
       </c>
-      <c r="C33" s="9" t="n">
+      <c r="C33" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D33" s="9" t="n">
+      <c r="D33" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E33" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>🟡</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>700104</t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>سيليكون ابيض 280 غم SK</t>
         </is>
       </c>
-      <c r="J33" s="9" t="n">
+      <c r="J33" s="6" t="n">
         <v>1.5</v>
       </c>
       <c r="K33" s="7" t="n"/>
-      <c r="L33" s="8" t="inlineStr">
-        <is>
-          <t>«سيليكون ابيض 280 غم SK» بـ1.5</t>
-        </is>
-      </c>
+      <c r="L33" s="5" t="inlineStr"/>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="4" t="n">
@@ -1966,7 +1969,7 @@
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
-          <t>🔴</t>
+          <t>⏸️</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
@@ -1983,7 +1986,7 @@
       <c r="K34" s="7" t="n"/>
       <c r="L34" s="10" t="inlineStr">
         <is>
-          <t>«متعدد الاستخدام» — بورسلان مفتوح بـ3؟ جرانيت بـ3؟</t>
+          <t>مؤجّل — عائلة اسطوانات القص (متعدد/حجر/حديد/زجاج/بورسلان × 4.5"/7"/9")</t>
         </is>
       </c>
     </row>
@@ -2219,45 +2222,47 @@
       <c r="A40" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="10" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>ربطة مواسير كهرباء 20ملم اسود</t>
         </is>
       </c>
-      <c r="C40" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="11" t="n">
+      <c r="C40" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="6" t="n">
         <v>25.5</v>
       </c>
       <c r="E40" s="4" t="n">
         <v>25.5</v>
       </c>
-      <c r="F40" s="11" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="G40" s="11" t="inlineStr">
-        <is>
-          <t>🔴</t>
-        </is>
-      </c>
-      <c r="H40" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I40" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J40" s="11" t="inlineStr"/>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>702741</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>ماسورة كهرباء 20ملم اسود - ربطة</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="n">
+        <v>14</v>
+      </c>
       <c r="K40" s="7" t="n"/>
-      <c r="L40" s="10" t="inlineStr">
-        <is>
-          <t>عندنا ربطة ماسورة كهرباء **25**ملم — الـ20ملم مش موجود</t>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>صنف جديد — بيع الكتالوج 14 · ⚠️ الفاتورة 25.500</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2291,7 @@
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>🔴</t>
+          <t>⏸️</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
@@ -2303,7 +2308,7 @@
       <c r="K41" s="7" t="n"/>
       <c r="L41" s="10" t="inlineStr">
         <is>
-          <t>عندنا مفة كهرباء **25**ملم — الـ20ملم مش موجود</t>
+          <t>مؤجّل — مع قائمة تأسيس الكهرباء</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2398,7 @@
       <c r="K43" s="7" t="n"/>
       <c r="L43" s="8" t="inlineStr">
         <is>
-          <t>نفس بند 9</t>
+          <t>نفس بند 3</t>
         </is>
       </c>
     </row>
@@ -2541,45 +2546,47 @@
       <c r="A47" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="10" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>منكوش يد بلاستك</t>
         </is>
       </c>
-      <c r="C47" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" s="11" t="n">
+      <c r="C47" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="6" t="n">
         <v>3</v>
       </c>
       <c r="E47" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F47" s="11" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="G47" s="11" t="inlineStr">
-        <is>
-          <t>🔴</t>
-        </is>
-      </c>
-      <c r="H47" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I47" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J47" s="11" t="inlineStr"/>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>700341</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>منكوش يد فيبر</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="n">
+        <v>4</v>
+      </c>
       <c r="K47" s="7" t="n"/>
-      <c r="L47" s="10" t="inlineStr">
-        <is>
-          <t>عندنا منكوش يد **فيبر** بـ4 — «بلاستك» مش موجود</t>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>منكوش يد فيبر</t>
         </is>
       </c>
     </row>
